--- a/_arquivos/ficha-conferencia-de-fontes.xlsx
+++ b/_arquivos/ficha-conferencia-de-fontes.xlsx
@@ -618,14 +618,42 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A margem média da distribuição industrial foi de 19,4% em 2024</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Panorama da Distribuição Industrial, 2025</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>O link dá erro e o título não aparece em busca nenhuma</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>sem data</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>não serve</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>linha removida do levantamento</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -818,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -831,9 +859,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -841,19 +867,15 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>As três primeiras linhas da outra aba são exemplo, e podem ser apagadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+          <t>As QUATRO primeiras linhas da outra aba são exemplo, e podem ser apagadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -882,9 +904,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -892,9 +912,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -906,6 +924,23 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>e é ela que vai para o seu material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>As quatro linhas de exemplo cobrem os três modos de falha e um caso que serve:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   a fonte que diz outra coisa · a fraca · a que confirma · a que não abre</t>
         </is>
       </c>
     </row>
